--- a/data/circular.xlsx
+++ b/data/circular.xlsx
@@ -1319,34 +1319,30 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45943.801</v>
+        <v>45943.79921492939</v>
       </c>
       <c r="B26" t="n">
-        <v>5624.4</v>
+        <v>5470.17</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.75</v>
+        <v>15.38</v>
       </c>
       <c r="E26" t="n">
         <v>0.01</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I26" t="b">
         <v>0</v>
@@ -1354,30 +1350,34 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45943.804</v>
+        <v>45943.801</v>
       </c>
       <c r="B27" t="n">
-        <v>5883.6</v>
+        <v>5624.4</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.38</v>
+        <v>15.75</v>
       </c>
       <c r="E27" t="n">
         <v>0.01</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H27" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -1385,34 +1385,30 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45943.807</v>
+        <v>45943.80221509484</v>
       </c>
       <c r="B28" t="n">
-        <v>6142.8</v>
+        <v>5729.38</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.97</v>
+        <v>15.51</v>
       </c>
       <c r="E28" t="n">
         <v>0.01</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -1420,10 +1416,10 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45943.807</v>
+        <v>45943.80521526037</v>
       </c>
       <c r="B29" t="n">
-        <v>6142.8</v>
+        <v>5988.6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1431,7 +1427,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.51</v>
+        <v>15.67</v>
       </c>
       <c r="E29" t="n">
         <v>0.01</v>
@@ -1451,30 +1447,34 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45943.81</v>
+        <v>45943.807</v>
       </c>
       <c r="B30" t="n">
-        <v>6402</v>
+        <v>6142.8</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.67</v>
+        <v>15.97</v>
       </c>
       <c r="E30" t="n">
         <v>0.01</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H30" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I30" t="b">
         <v>0</v>
@@ -1482,34 +1482,30 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45943.81090277778</v>
+        <v>45943.808215426</v>
       </c>
       <c r="B31" t="n">
-        <v>6480</v>
+        <v>6247.81</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LCO</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.7</v>
+        <v>15.73</v>
       </c>
       <c r="E31" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>3x200</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>42229</v>
+        <v>42333</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -1517,34 +1513,34 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45943.81155092592</v>
+        <v>45943.81090277778</v>
       </c>
       <c r="B32" t="n">
-        <v>6536</v>
+        <v>6480</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>OHP/T193</t>
+          <t>LCO</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.92</v>
+        <v>15.7</v>
       </c>
       <c r="E32" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>r'</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>3x200</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>42266</v>
+        <v>42229</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -1552,34 +1548,30 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45943.813</v>
+        <v>45943.81121559171</v>
       </c>
       <c r="B33" t="n">
-        <v>6661.2</v>
+        <v>6507.03</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16.09</v>
+        <v>15.74</v>
       </c>
       <c r="E33" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -1587,30 +1579,34 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45943.813</v>
+        <v>45943.81155092592</v>
       </c>
       <c r="B34" t="n">
-        <v>6661.2</v>
+        <v>6536</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>OHP/T193</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.73</v>
+        <v>15.92</v>
       </c>
       <c r="E34" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>r'</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="H34" t="n">
-        <v>42333</v>
+        <v>42266</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -1618,30 +1614,34 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45943.816</v>
+        <v>45943.813</v>
       </c>
       <c r="B35" t="n">
-        <v>6920.4</v>
+        <v>6661.2</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.74</v>
+        <v>16.09</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H35" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I35" t="b">
         <v>0</v>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45943.818</v>
+        <v>45943.81321570223</v>
       </c>
       <c r="B36" t="n">
-        <v>7093.2</v>
+        <v>6679.84</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1680,34 +1680,30 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45943.818</v>
+        <v>45943.8152158128</v>
       </c>
       <c r="B37" t="n">
-        <v>7093.2</v>
+        <v>6852.65</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16.16</v>
+        <v>15.86</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -1715,34 +1711,30 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45943.819</v>
+        <v>45943.8172159234</v>
       </c>
       <c r="B38" t="n">
-        <v>7179.6</v>
+        <v>7025.46</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>15.63</v>
+        <v>15.84</v>
       </c>
       <c r="E38" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I38" t="b">
         <v>0</v>
@@ -1750,18 +1742,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45943.819</v>
+        <v>45943.818</v>
       </c>
       <c r="B39" t="n">
-        <v>7179.6</v>
+        <v>7093.2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>15.63</v>
+        <v>16.16</v>
       </c>
       <c r="E39" t="n">
         <v>0.01</v>
@@ -1773,11 +1765,11 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I39" t="b">
         <v>0</v>
@@ -1785,34 +1777,34 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45943.81923611111</v>
+        <v>45943.819</v>
       </c>
       <c r="B40" t="n">
-        <v>7200</v>
+        <v>7179.6</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LCO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15.99</v>
+        <v>15.63</v>
       </c>
       <c r="E40" t="n">
         <v>0.01</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>3x200</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>42229</v>
+        <v>42262</v>
       </c>
       <c r="I40" t="b">
         <v>0</v>
@@ -1820,30 +1812,34 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45943.82</v>
+        <v>45943.819</v>
       </c>
       <c r="B41" t="n">
-        <v>7266</v>
+        <v>7179.6</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>15.86</v>
+        <v>15.63</v>
       </c>
       <c r="E41" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H41" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
@@ -1851,34 +1847,30 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45943.822</v>
+        <v>45943.81921603405</v>
       </c>
       <c r="B42" t="n">
-        <v>7438.8</v>
+        <v>7198.27</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15.67</v>
+        <v>15.84</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I42" t="b">
         <v>0</v>
@@ -1886,30 +1878,34 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45943.822</v>
+        <v>45943.81923611111</v>
       </c>
       <c r="B43" t="n">
-        <v>7438.8</v>
+        <v>7200</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>LCO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.84</v>
+        <v>15.99</v>
       </c>
       <c r="E43" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>3x200</t>
+        </is>
+      </c>
       <c r="H43" t="n">
-        <v>42333</v>
+        <v>42229</v>
       </c>
       <c r="I43" t="b">
         <v>0</v>
@@ -1917,34 +1913,34 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45943.82340277778</v>
+        <v>45943.822</v>
       </c>
       <c r="B44" t="n">
-        <v>7560</v>
+        <v>7438.8</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LCO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>16.3</v>
+        <v>15.67</v>
       </c>
       <c r="E44" t="n">
         <v>0.01</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3x200</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>42229</v>
+        <v>42262</v>
       </c>
       <c r="I44" t="b">
         <v>0</v>
@@ -1952,10 +1948,10 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45943.824</v>
+        <v>45943.82221620009</v>
       </c>
       <c r="B45" t="n">
-        <v>7611.6</v>
+        <v>7457.48</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1963,7 +1959,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>15.84</v>
+        <v>15.89</v>
       </c>
       <c r="E45" t="n">
         <v>0.02</v>
@@ -1983,34 +1979,34 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45943.824</v>
+        <v>45943.82340277778</v>
       </c>
       <c r="B46" t="n">
-        <v>7611.6</v>
+        <v>7560</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>LCO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="E46" t="n">
         <v>0.01</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>g</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>3x200</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>42275</v>
+        <v>42229</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
@@ -2018,34 +2014,34 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45943.82493055556</v>
+        <v>45943.824</v>
       </c>
       <c r="B47" t="n">
-        <v>7692</v>
+        <v>7611.6</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SAORAS</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>15.84</v>
+        <v>16.2</v>
       </c>
       <c r="E47" t="n">
         <v>0.01</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>42230</v>
+        <v>42275</v>
       </c>
       <c r="I47" t="b">
         <v>0</v>
@@ -2053,34 +2049,30 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45943.826</v>
+        <v>45943.82421631083</v>
       </c>
       <c r="B48" t="n">
-        <v>7784.4</v>
+        <v>7630.29</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>15.73</v>
+        <v>15.9</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I48" t="b">
         <v>0</v>
@@ -2088,30 +2080,34 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45943.827</v>
+        <v>45943.82493055556</v>
       </c>
       <c r="B49" t="n">
-        <v>7870.8</v>
+        <v>7692</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15.89</v>
+        <v>15.84</v>
       </c>
       <c r="E49" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>Rc</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
       <c r="H49" t="n">
-        <v>42333</v>
+        <v>42230</v>
       </c>
       <c r="I49" t="b">
         <v>0</v>
@@ -2119,30 +2115,34 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45943.829</v>
+        <v>45943.826</v>
       </c>
       <c r="B50" t="n">
-        <v>8043.6</v>
+        <v>7784.4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>15.9</v>
+        <v>15.73</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H50" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -2150,34 +2150,30 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45943.83</v>
+        <v>45943.82621642162</v>
       </c>
       <c r="B51" t="n">
-        <v>8130</v>
+        <v>7803.1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>15.72</v>
+        <v>15.92</v>
       </c>
       <c r="E51" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I51" t="b">
         <v>0</v>
@@ -2185,34 +2181,30 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45943.83</v>
+        <v>45943.82821653246</v>
       </c>
       <c r="B52" t="n">
-        <v>8130</v>
+        <v>7975.91</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>16.27</v>
+        <v>15.97</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I52" t="b">
         <v>0</v>
@@ -2220,30 +2212,34 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45943.831</v>
+        <v>45943.83</v>
       </c>
       <c r="B53" t="n">
-        <v>8216.4</v>
+        <v>8130</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>15.92</v>
+        <v>16.27</v>
       </c>
       <c r="E53" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H53" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I53" t="b">
         <v>0</v>
@@ -2251,30 +2247,34 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45943.833</v>
+        <v>45943.83</v>
       </c>
       <c r="B54" t="n">
-        <v>8389.200000000001</v>
+        <v>8130</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>15.97</v>
+        <v>15.72</v>
       </c>
       <c r="E54" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H54" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I54" t="b">
         <v>0</v>
@@ -2282,34 +2282,30 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45943.833</v>
+        <v>45943.83021664332</v>
       </c>
       <c r="B55" t="n">
-        <v>8389.200000000001</v>
+        <v>8148.72</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>15.77</v>
+        <v>15.96</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I55" t="b">
         <v>0</v>
@@ -2317,10 +2313,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45943.835</v>
+        <v>45943.83221675424</v>
       </c>
       <c r="B56" t="n">
-        <v>8562</v>
+        <v>8321.530000000001</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2328,7 +2324,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>15.96</v>
+        <v>16.04</v>
       </c>
       <c r="E56" t="n">
         <v>0.02</v>
@@ -2348,18 +2344,18 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45943.836</v>
+        <v>45943.833</v>
       </c>
       <c r="B57" t="n">
-        <v>8648.4</v>
+        <v>8389.200000000001</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>16.41</v>
+        <v>15.77</v>
       </c>
       <c r="E57" t="n">
         <v>0.01</v>
@@ -2371,11 +2367,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>42275</v>
+        <v>42262</v>
       </c>
       <c r="I57" t="b">
         <v>0</v>
@@ -2383,34 +2379,30 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45943.83613425926</v>
+        <v>45943.83421686519</v>
       </c>
       <c r="B58" t="n">
-        <v>8660</v>
+        <v>8494.34</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SAORAS</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>16.05</v>
+        <v>16.12</v>
       </c>
       <c r="E58" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>Rc</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>42230</v>
+        <v>42333</v>
       </c>
       <c r="I58" t="b">
         <v>0</v>
@@ -2418,34 +2410,34 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45943.837</v>
+        <v>45943.836</v>
       </c>
       <c r="B59" t="n">
-        <v>8734.799999999999</v>
+        <v>8648.4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OsservatorioAstronomicoNastroVerde</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>16.11</v>
+        <v>16.41</v>
       </c>
       <c r="E59" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>42269</v>
+        <v>42275</v>
       </c>
       <c r="I59" t="b">
         <v>0</v>
@@ -2453,34 +2445,34 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45943.837</v>
+        <v>45943.83613425926</v>
       </c>
       <c r="B60" t="n">
-        <v>8734.799999999999</v>
+        <v>8660</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>15.84</v>
+        <v>16.05</v>
       </c>
       <c r="E60" t="n">
         <v>0.01</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>42262</v>
+        <v>42230</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -2488,34 +2480,30 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45943.837</v>
+        <v>45943.83621697619</v>
       </c>
       <c r="B61" t="n">
-        <v>8734.799999999999</v>
+        <v>8667.15</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OsservatorioAstronomicoNastroVerde</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>16.58</v>
+        <v>16.12</v>
       </c>
       <c r="E61" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>42269</v>
+        <v>42333</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -2530,23 +2518,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>16.04</v>
+        <v>16.58</v>
       </c>
       <c r="E62" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H62" t="n">
-        <v>42333</v>
+        <v>42269</v>
       </c>
       <c r="I62" t="b">
         <v>0</v>
@@ -2554,30 +2546,34 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45943.839</v>
+        <v>45943.837</v>
       </c>
       <c r="B63" t="n">
-        <v>8907.6</v>
+        <v>8734.799999999999</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>16.12</v>
+        <v>15.84</v>
       </c>
       <c r="E63" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H63" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I63" t="b">
         <v>0</v>
@@ -2585,34 +2581,34 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45943.84</v>
+        <v>45943.837</v>
       </c>
       <c r="B64" t="n">
-        <v>8994</v>
+        <v>8734.799999999999</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>15.92</v>
+        <v>16.11</v>
       </c>
       <c r="E64" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>42262</v>
+        <v>42269</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
@@ -2620,10 +2616,10 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45943.841</v>
+        <v>45943.83821708722</v>
       </c>
       <c r="B65" t="n">
-        <v>9080.4</v>
+        <v>8839.959999999999</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2631,7 +2627,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>16.12</v>
+        <v>16.19</v>
       </c>
       <c r="E65" t="n">
         <v>0.02</v>
@@ -2651,18 +2647,18 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45943.841</v>
+        <v>45943.84</v>
       </c>
       <c r="B66" t="n">
-        <v>9080.4</v>
+        <v>8994</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16.53</v>
+        <v>15.92</v>
       </c>
       <c r="E66" t="n">
         <v>0.01</v>
@@ -2674,11 +2670,11 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>42275</v>
+        <v>42262</v>
       </c>
       <c r="I66" t="b">
         <v>0</v>
@@ -2686,10 +2682,10 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45943.843</v>
+        <v>45943.84021719831</v>
       </c>
       <c r="B67" t="n">
-        <v>9253.200000000001</v>
+        <v>9012.77</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2697,7 +2693,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.19</v>
+        <v>16.27</v>
       </c>
       <c r="E67" t="n">
         <v>0.02</v>
@@ -2717,18 +2713,18 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45943.844</v>
+        <v>45943.841</v>
       </c>
       <c r="B68" t="n">
-        <v>9339.6</v>
+        <v>9080.4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.98</v>
+        <v>16.53</v>
       </c>
       <c r="E68" t="n">
         <v>0.01</v>
@@ -2740,11 +2736,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I68" t="b">
         <v>0</v>
@@ -2752,34 +2748,30 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45943.84414351852</v>
+        <v>45943.84321736501</v>
       </c>
       <c r="B69" t="n">
-        <v>9352</v>
+        <v>9271.98</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SAORAS</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16.21</v>
+        <v>16.29</v>
       </c>
       <c r="E69" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
           <t>Rc</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>42230</v>
+        <v>42333</v>
       </c>
       <c r="I69" t="b">
         <v>0</v>
@@ -2787,30 +2779,34 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45943.845</v>
+        <v>45943.844</v>
       </c>
       <c r="B70" t="n">
-        <v>9426</v>
+        <v>9339.6</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16.27</v>
+        <v>15.98</v>
       </c>
       <c r="E70" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H70" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I70" t="b">
         <v>0</v>
@@ -2818,21 +2814,21 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45943.846</v>
+        <v>45943.84414351852</v>
       </c>
       <c r="B71" t="n">
-        <v>9512.4</v>
+        <v>9352</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OsservatorioAstronomicoNastroVerde</t>
+          <t>SAORAS</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>16.28</v>
+        <v>16.21</v>
       </c>
       <c r="E71" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2841,11 +2837,11 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>42269</v>
+        <v>42230</v>
       </c>
       <c r="I71" t="b">
         <v>0</v>
@@ -2853,10 +2849,10 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45943.847</v>
+        <v>45943.846</v>
       </c>
       <c r="B72" t="n">
-        <v>9598.799999999999</v>
+        <v>9512.4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2864,14 +2860,14 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>16.7</v>
+        <v>16.28</v>
       </c>
       <c r="E72" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2895,27 +2891,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16.61</v>
+        <v>16.7</v>
       </c>
       <c r="E73" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>42275</v>
+        <v>42269</v>
       </c>
       <c r="I73" t="b">
         <v>0</v>
@@ -2923,18 +2919,18 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45943.848</v>
+        <v>45943.847</v>
       </c>
       <c r="B74" t="n">
-        <v>9685.200000000001</v>
+        <v>9598.799999999999</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>16.05</v>
+        <v>16.61</v>
       </c>
       <c r="E74" t="n">
         <v>0.01</v>
@@ -2946,11 +2942,11 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I74" t="b">
         <v>0</v>
@@ -2965,23 +2961,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>16.29</v>
+        <v>16.05</v>
       </c>
       <c r="E75" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H75" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
@@ -2989,30 +2989,30 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45943.85048611111</v>
+        <v>45943.84821764306</v>
       </c>
       <c r="B76" t="n">
-        <v>9900</v>
+        <v>9704</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Asiago</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>16.51</v>
+        <v>15.94</v>
       </c>
       <c r="E76" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>Ic</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>42253</v>
+        <v>42333</v>
       </c>
       <c r="I76" t="b">
         <v>0</v>
@@ -3020,30 +3020,30 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45943.85048611111</v>
+        <v>45943.85021775435</v>
       </c>
       <c r="B77" t="n">
-        <v>9900</v>
+        <v>9876.809999999999</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Asiago</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>16.27</v>
+        <v>16.33</v>
       </c>
       <c r="E77" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>i</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>42253</v>
+        <v>42333</v>
       </c>
       <c r="I77" t="b">
         <v>0</v>
@@ -3051,34 +3051,30 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45943.851</v>
+        <v>45943.85048611111</v>
       </c>
       <c r="B78" t="n">
-        <v>9944.4</v>
+        <v>9900</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Asiago</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>16.12</v>
+        <v>16.51</v>
       </c>
       <c r="E78" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>42262</v>
+        <v>42253</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -3086,65 +3082,65 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45943.85203703704</v>
+        <v>45943.85048611111</v>
       </c>
       <c r="B79" t="n">
-        <v>10034</v>
+        <v>9900</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Asiago</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>18.6</v>
+        <v>16.27</v>
       </c>
       <c r="E79" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>i</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>42235</v>
+        <v>42253</v>
       </c>
       <c r="I79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45943.853</v>
+        <v>45943.851</v>
       </c>
       <c r="B80" t="n">
-        <v>10117.2</v>
+        <v>9944.4</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>15.94</v>
+        <v>16.12</v>
       </c>
       <c r="E80" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H80" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I80" t="b">
         <v>0</v>
@@ -3152,21 +3148,21 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45943.853</v>
+        <v>45943.85203703704</v>
       </c>
       <c r="B81" t="n">
-        <v>10117.2</v>
+        <v>10034</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>16.68</v>
+        <v>18.6</v>
       </c>
       <c r="E81" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -3175,68 +3171,64 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>42275</v>
+        <v>42235</v>
       </c>
       <c r="I81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45943.85311342592</v>
+        <v>45943.85221786569</v>
       </c>
       <c r="B82" t="n">
-        <v>10127</v>
+        <v>10049.62</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>18.7</v>
+        <v>15.95</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>42235</v>
+        <v>42333</v>
       </c>
       <c r="I82" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45943.85418981482</v>
+        <v>45943.853</v>
       </c>
       <c r="B83" t="n">
-        <v>10220</v>
+        <v>10117.2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>18.9</v>
+        <v>16.68</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3245,37 +3237,37 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>42235</v>
+        <v>42275</v>
       </c>
       <c r="I83" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45943.855</v>
+        <v>45943.85311342592</v>
       </c>
       <c r="B84" t="n">
-        <v>10290</v>
+        <v>10127</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OsservatorioAstronomicoNastroVerde</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>16.43</v>
+        <v>18.7</v>
       </c>
       <c r="E84" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3284,73 +3276,73 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>42269</v>
+        <v>42235</v>
       </c>
       <c r="I84" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45943.855</v>
+        <v>45943.85418981482</v>
       </c>
       <c r="B85" t="n">
-        <v>10290</v>
+        <v>10220</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>16.33</v>
+        <v>18.9</v>
       </c>
       <c r="E85" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H85" t="n">
-        <v>42333</v>
+        <v>42235</v>
       </c>
       <c r="I85" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45943.855</v>
+        <v>45943.85421797707</v>
       </c>
       <c r="B86" t="n">
-        <v>10290</v>
+        <v>10222.43</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>16.18</v>
+        <v>16.34</v>
       </c>
       <c r="E86" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I86" t="b">
         <v>0</v>
@@ -3358,21 +3350,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45943.85528935185</v>
+        <v>45943.855</v>
       </c>
       <c r="B87" t="n">
-        <v>10315</v>
+        <v>10290</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>18.8</v>
+        <v>16.18</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3381,46 +3373,46 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I87" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45943.85590277778</v>
+        <v>45943.855</v>
       </c>
       <c r="B88" t="n">
-        <v>10368</v>
+        <v>10290</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NOT</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>16.52</v>
+        <v>16.43</v>
       </c>
       <c r="E88" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>30 sec</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>42227</v>
+        <v>42269</v>
       </c>
       <c r="I88" t="b">
         <v>0</v>
@@ -3428,69 +3420,69 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45943.856</v>
+        <v>45943.85528935185</v>
       </c>
       <c r="B89" t="n">
-        <v>10376.4</v>
+        <v>10315</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>LCO</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>16.61</v>
+        <v>18.8</v>
       </c>
       <c r="E89" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>422561</v>
+        <v>42235</v>
       </c>
       <c r="I89" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45943.856</v>
+        <v>45943.85590277778</v>
       </c>
       <c r="B90" t="n">
-        <v>10376.4</v>
+        <v>10368</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OsservatorioAstronomicoNastroVerde</t>
+          <t>NOT</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>16.9</v>
+        <v>16.52</v>
       </c>
       <c r="E90" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>r</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30 sec</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>42269</v>
+        <v>42227</v>
       </c>
       <c r="I90" t="b">
         <v>0</v>
@@ -3498,65 +3490,69 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45943.85638888889</v>
+        <v>45943.856</v>
       </c>
       <c r="B91" t="n">
-        <v>10410</v>
+        <v>10376.4</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>LCO</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>18.7</v>
+        <v>16.61</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>42235</v>
+        <v>422561</v>
       </c>
       <c r="I91" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45943.857</v>
+        <v>45943.856</v>
       </c>
       <c r="B92" t="n">
-        <v>10462.8</v>
+        <v>10376.4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>15.95</v>
+        <v>16.9</v>
       </c>
       <c r="E92" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H92" t="n">
-        <v>42333</v>
+        <v>42269</v>
       </c>
       <c r="I92" t="b">
         <v>0</v>
@@ -3564,99 +3560,103 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45943.85752314814</v>
+        <v>45943.85621808851</v>
       </c>
       <c r="B93" t="n">
-        <v>10508</v>
+        <v>10395.24</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>18.6</v>
+        <v>15.92</v>
       </c>
       <c r="E93" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>42235</v>
+        <v>42333</v>
       </c>
       <c r="I93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45943.85856481481</v>
+        <v>45943.85638888889</v>
       </c>
       <c r="B94" t="n">
-        <v>10598</v>
+        <v>10410</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>INO340</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>16.3</v>
+        <v>18.7</v>
       </c>
       <c r="E94" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>i</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H94" t="n">
-        <v>42492</v>
+        <v>42235</v>
       </c>
       <c r="I94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45943.85856481481</v>
+        <v>45943.85752314814</v>
       </c>
       <c r="B95" t="n">
-        <v>10598</v>
+        <v>10508</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>INO340</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>16.63</v>
+        <v>18.6</v>
       </c>
       <c r="E95" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>r</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H95" t="n">
-        <v>42492</v>
+        <v>42235</v>
       </c>
       <c r="I95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -3672,14 +3672,14 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>16.75</v>
+        <v>16.3</v>
       </c>
       <c r="E96" t="n">
         <v>0.02</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>g</t>
+          <t>i</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -3692,69 +3692,61 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45943.85862268518</v>
+        <v>45943.85856481481</v>
       </c>
       <c r="B97" t="n">
-        <v>10603</v>
+        <v>10598</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>INO340</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>18.9</v>
+        <v>16.63</v>
       </c>
       <c r="E97" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>42235</v>
+        <v>42492</v>
       </c>
       <c r="I97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45943.859</v>
+        <v>45943.85856481481</v>
       </c>
       <c r="B98" t="n">
-        <v>10635.6</v>
+        <v>10598</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>INO340</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>16.69</v>
+        <v>16.75</v>
       </c>
       <c r="E98" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>g</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>42275</v>
+        <v>42492</v>
       </c>
       <c r="I98" t="b">
         <v>0</v>
@@ -3762,21 +3754,21 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45943.859</v>
+        <v>45943.85862268518</v>
       </c>
       <c r="B99" t="n">
-        <v>10635.6</v>
+        <v>10603</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>16.24</v>
+        <v>18.9</v>
       </c>
       <c r="E99" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3785,14 +3777,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>42262</v>
+        <v>42235</v>
       </c>
       <c r="I99" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -3804,23 +3796,27 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>16.34</v>
+        <v>16.69</v>
       </c>
       <c r="E100" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H100" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I100" t="b">
         <v>0</v>
@@ -3828,21 +3824,21 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45943.86039351852</v>
+        <v>45943.859</v>
       </c>
       <c r="B101" t="n">
-        <v>10756</v>
+        <v>10635.6</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>18.8</v>
+        <v>16.24</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3851,22 +3847,22 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45943.861</v>
+        <v>45943.85921825573</v>
       </c>
       <c r="B102" t="n">
-        <v>10808.4</v>
+        <v>10654.46</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -3874,14 +3870,14 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>15.92</v>
+        <v>16.37</v>
       </c>
       <c r="E102" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ic</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -3894,21 +3890,21 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45943.862</v>
+        <v>45943.86039351852</v>
       </c>
       <c r="B103" t="n">
-        <v>10894.8</v>
+        <v>10756</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>16.24</v>
+        <v>18.8</v>
       </c>
       <c r="E103" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3917,77 +3913,77 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>42262</v>
+        <v>42235</v>
       </c>
       <c r="I103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45943.86229166666</v>
+        <v>45943.86121836726</v>
       </c>
       <c r="B104" t="n">
-        <v>10920</v>
+        <v>10827.27</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>19</v>
+        <v>15.86</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>42235</v>
+        <v>42333</v>
       </c>
       <c r="I104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45943.864</v>
+        <v>45943.862</v>
       </c>
       <c r="B105" t="n">
-        <v>11067.6</v>
+        <v>10894.8</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>16.37</v>
+        <v>16.24</v>
       </c>
       <c r="E105" t="n">
         <v>0.02</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H105" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I105" t="b">
         <v>0</v>
@@ -3995,80 +3991,76 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45943.864</v>
+        <v>45943.86229166666</v>
       </c>
       <c r="B106" t="n">
-        <v>11067.6</v>
+        <v>10920</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>OsservatorioAstronomicoNastroVerde</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="E106" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>42269</v>
+        <v>42235</v>
       </c>
       <c r="I106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45943.86408564815</v>
+        <v>45943.86321847884</v>
       </c>
       <c r="B107" t="n">
-        <v>11075</v>
+        <v>11000.08</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>19</v>
+        <v>16.41</v>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
-        <v>42235</v>
+        <v>42333</v>
       </c>
       <c r="I107" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45943.865</v>
+        <v>45943.864</v>
       </c>
       <c r="B108" t="n">
-        <v>11154</v>
+        <v>11067.6</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -4076,14 +4068,14 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>17.26</v>
+        <v>16.5</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4100,21 +4092,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45943.865</v>
+        <v>45943.86408564815</v>
       </c>
       <c r="B109" t="n">
-        <v>11154</v>
+        <v>11075</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>16.72</v>
+        <v>19</v>
       </c>
       <c r="E109" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4123,33 +4115,33 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>42275</v>
+        <v>42235</v>
       </c>
       <c r="I109" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45943.86590277778</v>
+        <v>45943.865</v>
       </c>
       <c r="B110" t="n">
-        <v>11232</v>
+        <v>11154</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>19.2</v>
+        <v>16.72</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4158,42 +4150,46 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>42235</v>
+        <v>42275</v>
       </c>
       <c r="I110" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45943.866</v>
+        <v>45943.865</v>
       </c>
       <c r="B111" t="n">
-        <v>11240.4</v>
+        <v>11154</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>OsservatorioAstronomicoNastroVerde</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>15.86</v>
+        <v>17.26</v>
       </c>
       <c r="E111" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="H111" t="n">
-        <v>42333</v>
+        <v>42269</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -4201,34 +4197,30 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45943.866</v>
+        <v>45943.86521859046</v>
       </c>
       <c r="B112" t="n">
-        <v>11240.4</v>
+        <v>11172.89</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>16.24</v>
+        <v>16.05</v>
       </c>
       <c r="E112" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I112" t="b">
         <v>0</v>
@@ -4236,10 +4228,10 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45943.86767361111</v>
+        <v>45943.86590277778</v>
       </c>
       <c r="B113" t="n">
-        <v>11385</v>
+        <v>11232</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -4271,30 +4263,34 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45943.868</v>
+        <v>45943.866</v>
       </c>
       <c r="B114" t="n">
-        <v>11413.2</v>
+        <v>11240.4</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>16.41</v>
+        <v>16.24</v>
       </c>
       <c r="E114" t="n">
         <v>0.02</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H114" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I114" t="b">
         <v>0</v>
@@ -4302,34 +4298,30 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45943.86840277778</v>
+        <v>45943.86721870213</v>
       </c>
       <c r="B115" t="n">
-        <v>11448</v>
+        <v>11345.7</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kilonova-Catcher</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>16.29</v>
+        <v>16.56</v>
       </c>
       <c r="E115" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
           <t>Rc</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>30x30</t>
-        </is>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
-        <v>42301</v>
+        <v>42333</v>
       </c>
       <c r="I115" t="b">
         <v>0</v>
@@ -4337,10 +4329,10 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45943.86945601852</v>
+        <v>45943.86767361111</v>
       </c>
       <c r="B116" t="n">
-        <v>11539</v>
+        <v>11385</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -4360,7 +4352,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H116" t="n">
@@ -4372,34 +4364,34 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45943.87</v>
+        <v>45943.86840277778</v>
       </c>
       <c r="B117" t="n">
-        <v>11586</v>
+        <v>11448</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Kilonova-Catcher</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>16.29</v>
       </c>
       <c r="E117" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>30x30</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>42262</v>
+        <v>42301</v>
       </c>
       <c r="I117" t="b">
         <v>0</v>
@@ -4407,10 +4399,10 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45943.87</v>
+        <v>45943.86921881384</v>
       </c>
       <c r="B118" t="n">
-        <v>11586</v>
+        <v>11518.51</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -4418,7 +4410,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>16.05</v>
+        <v>16.25</v>
       </c>
       <c r="E118" t="n">
         <v>0.04</v>
@@ -4438,21 +4430,21 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45943.87</v>
+        <v>45943.86945601852</v>
       </c>
       <c r="B119" t="n">
-        <v>11586</v>
+        <v>11539</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>16.8</v>
+        <v>19.2</v>
       </c>
       <c r="E119" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4461,44 +4453,46 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>42275</v>
+        <v>42235</v>
       </c>
       <c r="I119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>45943.87149305556</v>
+        <v>45943.87</v>
       </c>
       <c r="B120" t="n">
-        <v>11715</v>
+        <v>11586</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VTP</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.01</v>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>42228</v>
+        <v>42275</v>
       </c>
       <c r="I120" t="b">
         <v>0</v>
@@ -4506,21 +4500,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>45943.87197916667</v>
+        <v>45943.87</v>
       </c>
       <c r="B121" t="n">
-        <v>11757</v>
+        <v>11586</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>19.2</v>
+        <v>16.29</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4529,22 +4523,22 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I121" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>45943.872</v>
+        <v>45943.8712189256</v>
       </c>
       <c r="B122" t="n">
-        <v>11758.8</v>
+        <v>11691.32</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -4552,7 +4546,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>16.56</v>
+        <v>16.46</v>
       </c>
       <c r="E122" t="n">
         <v>0.03</v>
@@ -4572,30 +4566,32 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>45943.87283564815</v>
+        <v>45943.87149305556</v>
       </c>
       <c r="B123" t="n">
-        <v>11831</v>
+        <v>11715</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ABObservatory</t>
+          <t>VTP</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="E123" t="n">
-        <v>0.06</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="H123" t="n">
-        <v>42251</v>
+        <v>42228</v>
       </c>
       <c r="I123" t="b">
         <v>0</v>
@@ -4603,21 +4599,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>45943.873</v>
+        <v>45943.87197916667</v>
       </c>
       <c r="B124" t="n">
-        <v>11845.2</v>
+        <v>11757</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>16.31</v>
+        <v>19.2</v>
       </c>
       <c r="E124" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -4626,42 +4622,42 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>42262</v>
+        <v>42235</v>
       </c>
       <c r="I124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>45943.874</v>
+        <v>45943.87283564815</v>
       </c>
       <c r="B125" t="n">
-        <v>11931.6</v>
+        <v>11831</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>ABObservatory</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>16.25</v>
+        <v>16.86</v>
       </c>
       <c r="E125" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ic</t>
+          <t>V</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
-        <v>42333</v>
+        <v>42251</v>
       </c>
       <c r="I125" t="b">
         <v>0</v>
@@ -4669,21 +4665,21 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>45943.87447916667</v>
+        <v>45943.873</v>
       </c>
       <c r="B126" t="n">
-        <v>11973</v>
+        <v>11845.2</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>19.4</v>
+        <v>16.31</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -4692,33 +4688,33 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I126" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>45943.876</v>
+        <v>45943.87447916667</v>
       </c>
       <c r="B127" t="n">
-        <v>12104.4</v>
+        <v>11973</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>16.8</v>
+        <v>19.4</v>
       </c>
       <c r="E127" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -4727,14 +4723,14 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>180</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>42275</v>
+        <v>42235</v>
       </c>
       <c r="I127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -4746,23 +4742,27 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>16.46</v>
+        <v>16.8</v>
       </c>
       <c r="E128" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H128" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H131" t="n">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H132" t="n">
@@ -5015,56 +5015,52 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>45943.88244212963</v>
+        <v>45943.88221954105</v>
       </c>
       <c r="B136" t="n">
-        <v>12661</v>
+        <v>12641.77</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>19.7</v>
+        <v>16.14</v>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
-        <v>42235</v>
+        <v>42333</v>
       </c>
       <c r="I136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>45943.884</v>
+        <v>45943.88244212963</v>
       </c>
       <c r="B137" t="n">
-        <v>12795.6</v>
+        <v>12661</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>16.37</v>
+        <v>19.7</v>
       </c>
       <c r="E137" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -5073,33 +5069,33 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>42262</v>
+        <v>42235</v>
       </c>
       <c r="I137" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>45943.88421296296</v>
+        <v>45943.884</v>
       </c>
       <c r="B138" t="n">
-        <v>12814</v>
+        <v>12795.6</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>20.4</v>
+        <v>16.37</v>
       </c>
       <c r="E138" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -5108,14 +5104,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -5155,10 +5151,10 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>45943.88600694444</v>
+        <v>45943.88421296296</v>
       </c>
       <c r="B140" t="n">
-        <v>12969</v>
+        <v>12814</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -5166,7 +5162,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>19.7</v>
+        <v>20.4</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -5178,7 +5174,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H140" t="n">
@@ -5190,10 +5186,10 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>45943.887</v>
+        <v>45943.8842196531</v>
       </c>
       <c r="B141" t="n">
-        <v>13054.8</v>
+        <v>12814.58</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -5201,14 +5197,14 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>16.14</v>
+        <v>16.64</v>
       </c>
       <c r="E141" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ic</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -5221,10 +5217,10 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>45943.88791666667</v>
+        <v>45943.88600694444</v>
       </c>
       <c r="B142" t="n">
-        <v>13134</v>
+        <v>12969</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -5232,7 +5228,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -5256,34 +5252,30 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>45943.888</v>
+        <v>45943.8862197652</v>
       </c>
       <c r="B143" t="n">
-        <v>13141.2</v>
+        <v>12987.39</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>16.43</v>
+        <v>16.19</v>
       </c>
       <c r="E143" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I143" t="b">
         <v>0</v>
@@ -5291,21 +5283,21 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>45943.888</v>
+        <v>45943.88791666667</v>
       </c>
       <c r="B144" t="n">
-        <v>13141.2</v>
+        <v>13134</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>16.91</v>
+        <v>19.6</v>
       </c>
       <c r="E144" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -5314,42 +5306,46 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>42275</v>
+        <v>42235</v>
       </c>
       <c r="I144" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>45943.889</v>
+        <v>45943.888</v>
       </c>
       <c r="B145" t="n">
-        <v>13227.6</v>
+        <v>13141.2</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>16.64</v>
+        <v>16.91</v>
       </c>
       <c r="E145" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H145" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I145" t="b">
         <v>0</v>
@@ -5357,21 +5353,21 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>45943.8896875</v>
+        <v>45943.888</v>
       </c>
       <c r="B146" t="n">
-        <v>13287</v>
+        <v>13141.2</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>19.9</v>
+        <v>16.43</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -5380,46 +5376,42 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>45943.891</v>
+        <v>45943.88821987733</v>
       </c>
       <c r="B147" t="n">
-        <v>13400.4</v>
+        <v>13160.2</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>16.47</v>
+        <v>16.54</v>
       </c>
       <c r="E147" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I147" t="b">
         <v>0</v>
@@ -5427,52 +5419,56 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>45943.891</v>
+        <v>45943.8896875</v>
       </c>
       <c r="B148" t="n">
-        <v>13400.4</v>
+        <v>13287</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>16.19</v>
+        <v>19.9</v>
       </c>
       <c r="E148" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="H148" t="n">
-        <v>42333</v>
+        <v>42235</v>
       </c>
       <c r="I148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>45943.89148148148</v>
+        <v>45943.891</v>
       </c>
       <c r="B149" t="n">
-        <v>13442</v>
+        <v>13400.4</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>19.8</v>
+        <v>16.47</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -5481,22 +5477,22 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I149" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>45943.893</v>
+        <v>45943.89122004561</v>
       </c>
       <c r="B150" t="n">
-        <v>13573.2</v>
+        <v>13419.41</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -5504,14 +5500,14 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>16.54</v>
+        <v>16.33</v>
       </c>
       <c r="E150" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>Ic</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -5524,21 +5520,21 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>45943.893</v>
+        <v>45943.89148148148</v>
       </c>
       <c r="B151" t="n">
-        <v>13573.2</v>
+        <v>13442</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>17.02</v>
+        <v>19.8</v>
       </c>
       <c r="E151" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -5547,33 +5543,33 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>42275</v>
+        <v>42235</v>
       </c>
       <c r="I151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>45943.895</v>
+        <v>45943.893</v>
       </c>
       <c r="B152" t="n">
-        <v>13746</v>
+        <v>13573.2</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>16.54</v>
+        <v>17.02</v>
       </c>
       <c r="E152" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -5582,11 +5578,11 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I152" t="b">
         <v>0</v>
@@ -5594,10 +5590,10 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>45943.896</v>
+        <v>45943.89322015787</v>
       </c>
       <c r="B153" t="n">
-        <v>13832.4</v>
+        <v>13592.22</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -5605,14 +5601,14 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>16.33</v>
+        <v>16.69</v>
       </c>
       <c r="E153" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ic</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
@@ -5625,30 +5621,34 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>45943.898</v>
+        <v>45943.895</v>
       </c>
       <c r="B154" t="n">
-        <v>14005.2</v>
+        <v>13746</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>16.69</v>
+        <v>16.54</v>
       </c>
       <c r="E154" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H154" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I154" t="b">
         <v>0</v>
@@ -5656,34 +5656,30 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>45943.899</v>
+        <v>45943.89522027016</v>
       </c>
       <c r="B155" t="n">
-        <v>14091.6</v>
+        <v>13765.03</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>16.55</v>
+        <v>16.23</v>
       </c>
       <c r="E155" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
       <c r="H155" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I155" t="b">
         <v>0</v>
@@ -5698,14 +5694,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>17.02</v>
+        <v>16.55</v>
       </c>
       <c r="E156" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -5714,11 +5710,11 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>42275</v>
+        <v>42262</v>
       </c>
       <c r="I156" t="b">
         <v>0</v>
@@ -5726,30 +5722,34 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>45943.9</v>
+        <v>45943.899</v>
       </c>
       <c r="B157" t="n">
-        <v>14178</v>
+        <v>14091.6</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>16.23</v>
+        <v>17.02</v>
       </c>
       <c r="E157" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H157" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I157" t="b">
         <v>0</v>
@@ -5757,34 +5757,30 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>45943.902</v>
+        <v>45943.89922049488</v>
       </c>
       <c r="B158" t="n">
-        <v>14350.8</v>
+        <v>14110.65</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>16.56</v>
+        <v>16.37</v>
       </c>
       <c r="E158" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I158" t="b">
         <v>0</v>
@@ -5792,34 +5788,30 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>45943.90284722222</v>
+        <v>45943.9012206073</v>
       </c>
       <c r="B159" t="n">
-        <v>14424</v>
+        <v>14283.46</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>GOTO</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>17.11</v>
+        <v>16.8</v>
       </c>
       <c r="E159" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>4x45s</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="n">
-        <v>42231</v>
+        <v>42333</v>
       </c>
       <c r="I159" t="b">
         <v>0</v>
@@ -5827,34 +5819,34 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>45943.90321759259</v>
+        <v>45943.902</v>
       </c>
       <c r="B160" t="n">
-        <v>14456</v>
+        <v>14350.8</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>ISON-Castelgrande</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>16.75</v>
+        <v>16.56</v>
       </c>
       <c r="E160" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>15*60</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>42396</v>
+        <v>42262</v>
       </c>
       <c r="I160" t="b">
         <v>0</v>
@@ -5862,30 +5854,34 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>45943.904</v>
+        <v>45943.90284722222</v>
       </c>
       <c r="B161" t="n">
-        <v>14523.6</v>
+        <v>14424</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>GOTO</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>16.37</v>
+        <v>17.11</v>
       </c>
       <c r="E161" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>4x45s</t>
+        </is>
+      </c>
       <c r="H161" t="n">
-        <v>42333</v>
+        <v>42231</v>
       </c>
       <c r="I161" t="b">
         <v>0</v>
@@ -5893,34 +5889,34 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>45943.905</v>
+        <v>45943.90321759259</v>
       </c>
       <c r="B162" t="n">
-        <v>14610</v>
+        <v>14456</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>ISON-Castelgrande</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>17.17</v>
+        <v>16.75</v>
       </c>
       <c r="E162" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>Clear</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>15*60</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>42275</v>
+        <v>42396</v>
       </c>
       <c r="I162" t="b">
         <v>0</v>
@@ -5928,34 +5924,30 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>45943.906</v>
+        <v>45943.90322071978</v>
       </c>
       <c r="B163" t="n">
-        <v>14696.4</v>
+        <v>14456.27</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>16.61</v>
+        <v>16.4</v>
       </c>
       <c r="E163" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I163" t="b">
         <v>0</v>
@@ -5963,30 +5955,34 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>45943.906</v>
+        <v>45943.905</v>
       </c>
       <c r="B164" t="n">
-        <v>14696.4</v>
+        <v>14610</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>16.8</v>
+        <v>17.17</v>
       </c>
       <c r="E164" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H164" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I164" t="b">
         <v>0</v>
@@ -5994,10 +5990,10 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>45943.908</v>
+        <v>45943.90522083229</v>
       </c>
       <c r="B165" t="n">
-        <v>14869.2</v>
+        <v>14629.08</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -6005,14 +6001,14 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>16.4</v>
+        <v>16.75</v>
       </c>
       <c r="E165" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ic</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G165" t="inlineStr"/>
@@ -6025,30 +6021,34 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>45943.91</v>
+        <v>45943.906</v>
       </c>
       <c r="B166" t="n">
-        <v>15042</v>
+        <v>14696.4</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>16.75</v>
+        <v>16.61</v>
       </c>
       <c r="E166" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H166" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I166" t="b">
         <v>0</v>
@@ -6056,34 +6056,30 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>45943.91</v>
+        <v>45943.90822100115</v>
       </c>
       <c r="B167" t="n">
-        <v>15042</v>
+        <v>14888.29</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>16.64</v>
+        <v>16.43</v>
       </c>
       <c r="E167" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I167" t="b">
         <v>0</v>
@@ -6091,18 +6087,18 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>45943.911</v>
+        <v>45943.91</v>
       </c>
       <c r="B168" t="n">
-        <v>15128.4</v>
+        <v>15042</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>17.17</v>
+        <v>16.64</v>
       </c>
       <c r="E168" t="n">
         <v>0.02</v>
@@ -6114,11 +6110,11 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>42275</v>
+        <v>42262</v>
       </c>
       <c r="I168" t="b">
         <v>0</v>
@@ -6126,34 +6122,30 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>45943.913</v>
+        <v>45943.91022111379</v>
       </c>
       <c r="B169" t="n">
-        <v>15301.2</v>
+        <v>15061.1</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>16.64</v>
+        <v>16.93</v>
       </c>
       <c r="E169" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I169" t="b">
         <v>0</v>
@@ -6161,30 +6153,34 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>45943.913</v>
+        <v>45943.911</v>
       </c>
       <c r="B170" t="n">
-        <v>15301.2</v>
+        <v>15128.4</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>16.43</v>
+        <v>17.17</v>
       </c>
       <c r="E170" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H170" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I170" t="b">
         <v>0</v>
@@ -6192,34 +6188,30 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>45943.91443287037</v>
+        <v>45943.91222122646</v>
       </c>
       <c r="B171" t="n">
-        <v>15425</v>
+        <v>15233.91</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>ISON-Castelgrande</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>16.86</v>
+        <v>16.24</v>
       </c>
       <c r="E171" t="n">
-        <v>0.08</v>
+        <v>0.05</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>15*60</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
       <c r="H171" t="n">
-        <v>42396</v>
+        <v>42333</v>
       </c>
       <c r="I171" t="b">
         <v>0</v>
@@ -6227,30 +6219,34 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>45943.915</v>
+        <v>45943.913</v>
       </c>
       <c r="B172" t="n">
-        <v>15474</v>
+        <v>15301.2</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>16.93</v>
+        <v>16.64</v>
       </c>
       <c r="E172" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H172" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I172" t="b">
         <v>0</v>
@@ -6258,34 +6254,30 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>45943.917</v>
+        <v>45943.91422133917</v>
       </c>
       <c r="B173" t="n">
-        <v>15646.8</v>
+        <v>15406.72</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>16.68</v>
+        <v>16.82</v>
       </c>
       <c r="E173" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Rc</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
       <c r="H173" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I173" t="b">
         <v>0</v>
@@ -6293,30 +6285,34 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>45943.917</v>
+        <v>45943.91443287037</v>
       </c>
       <c r="B174" t="n">
-        <v>15646.8</v>
+        <v>15425</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>ISON-Castelgrande</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>16.24</v>
+        <v>16.86</v>
       </c>
       <c r="E174" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr"/>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>15*60</t>
+        </is>
+      </c>
       <c r="H174" t="n">
-        <v>42333</v>
+        <v>42396</v>
       </c>
       <c r="I174" t="b">
         <v>0</v>
@@ -6324,34 +6320,30 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>45943.917</v>
+        <v>45943.91622145193</v>
       </c>
       <c r="B175" t="n">
-        <v>15646.8</v>
+        <v>15579.53</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>17.22</v>
+        <v>16.42</v>
       </c>
       <c r="E175" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>8x60s</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
       <c r="H175" t="n">
-        <v>42275</v>
+        <v>42333</v>
       </c>
       <c r="I175" t="b">
         <v>0</v>
@@ -6359,30 +6351,34 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>45943.919</v>
+        <v>45943.917</v>
       </c>
       <c r="B176" t="n">
-        <v>15819.6</v>
+        <v>15646.8</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>16.82</v>
+        <v>16.68</v>
       </c>
       <c r="E176" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H176" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I176" t="b">
         <v>0</v>
@@ -6390,18 +6386,18 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>45943.92</v>
+        <v>45943.917</v>
       </c>
       <c r="B177" t="n">
-        <v>15906</v>
+        <v>15646.8</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>16.71</v>
+        <v>17.22</v>
       </c>
       <c r="E177" t="n">
         <v>0.02</v>
@@ -6413,11 +6409,11 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H177" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I177" t="b">
         <v>0</v>
@@ -6425,10 +6421,10 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>45943.921</v>
+        <v>45943.91822156475</v>
       </c>
       <c r="B178" t="n">
-        <v>15992.4</v>
+        <v>15752.34</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -6436,14 +6432,14 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>16.42</v>
+        <v>16.72</v>
       </c>
       <c r="E178" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ic</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G178" t="inlineStr"/>
@@ -6456,18 +6452,18 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>45943.922</v>
+        <v>45943.92</v>
       </c>
       <c r="B179" t="n">
-        <v>16078.8</v>
+        <v>15906</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>17.23</v>
+        <v>16.71</v>
       </c>
       <c r="E179" t="n">
         <v>0.02</v>
@@ -6479,11 +6475,11 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H179" t="n">
-        <v>42275</v>
+        <v>42262</v>
       </c>
       <c r="I179" t="b">
         <v>0</v>
@@ -6491,10 +6487,10 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>45943.923</v>
+        <v>45943.9202216776</v>
       </c>
       <c r="B180" t="n">
-        <v>16165.2</v>
+        <v>15925.15</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -6502,14 +6498,14 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>16.72</v>
+        <v>16.49</v>
       </c>
       <c r="E180" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rc</t>
+          <t>Ic</t>
         </is>
       </c>
       <c r="G180" t="inlineStr"/>
@@ -6522,18 +6518,18 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>45943.924</v>
+        <v>45943.922</v>
       </c>
       <c r="B181" t="n">
-        <v>16251.6</v>
+        <v>16078.8</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>16.78</v>
+        <v>17.23</v>
       </c>
       <c r="E181" t="n">
         <v>0.02</v>
@@ -6545,11 +6541,11 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>10x30</t>
+          <t>8x60s</t>
         </is>
       </c>
       <c r="H181" t="n">
-        <v>42262</v>
+        <v>42275</v>
       </c>
       <c r="I181" t="b">
         <v>0</v>
@@ -6557,10 +6553,10 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>45943.925</v>
+        <v>45943.92322184695</v>
       </c>
       <c r="B182" t="n">
-        <v>16338</v>
+        <v>16184.37</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -6568,14 +6564,14 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>16.49</v>
+        <v>17.11</v>
       </c>
       <c r="E182" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Ic</t>
+          <t>Rc</t>
         </is>
       </c>
       <c r="G182" t="inlineStr"/>
@@ -6588,21 +6584,21 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>45943.92641203704</v>
+        <v>45943.924</v>
       </c>
       <c r="B183" t="n">
-        <v>16460</v>
+        <v>16251.6</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>MASTER-SAAO</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>18.9</v>
+        <v>16.78</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -6611,46 +6607,42 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10x30</t>
         </is>
       </c>
       <c r="H183" t="n">
-        <v>42235</v>
+        <v>42262</v>
       </c>
       <c r="I183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>45943.92717592593</v>
+        <v>45943.92522195991</v>
       </c>
       <c r="B184" t="n">
-        <v>16526</v>
+        <v>16357.18</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>ISON-Castelgrande</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>17</v>
+        <v>16.68</v>
       </c>
       <c r="E184" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20*60</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
       <c r="H184" t="n">
-        <v>42396</v>
+        <v>42333</v>
       </c>
       <c r="I184" t="b">
         <v>0</v>
@@ -6658,21 +6650,21 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>45943.928</v>
+        <v>45943.92641203704</v>
       </c>
       <c r="B185" t="n">
-        <v>16597.2</v>
+        <v>16460</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Calapai</t>
+          <t>MASTER-SAAO</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>17.31</v>
+        <v>18.9</v>
       </c>
       <c r="E185" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -6681,42 +6673,46 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>8x60s</t>
+          <t>60</t>
         </is>
       </c>
       <c r="H185" t="n">
-        <v>42275</v>
+        <v>42235</v>
       </c>
       <c r="I185" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>45943.928</v>
+        <v>45943.92717592593</v>
       </c>
       <c r="B186" t="n">
-        <v>16597.2</v>
+        <v>16526</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>ISON-Castelgrande</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>17.11</v>
+        <v>17</v>
       </c>
       <c r="E186" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Rc</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr"/>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>20*60</t>
+        </is>
+      </c>
       <c r="H186" t="n">
-        <v>42333</v>
+        <v>42396</v>
       </c>
       <c r="I186" t="b">
         <v>0</v>
@@ -6759,30 +6755,34 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>45943.93</v>
+        <v>45943.928</v>
       </c>
       <c r="B188" t="n">
-        <v>16770</v>
+        <v>16597.2</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>Calapai</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>16.68</v>
+        <v>17.31</v>
       </c>
       <c r="E188" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>8x60s</t>
+        </is>
+      </c>
       <c r="H188" t="n">
-        <v>42333</v>
+        <v>42275</v>
       </c>
       <c r="I188" t="b">
         <v>0</v>
@@ -6790,34 +6790,30 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>45943.931</v>
+        <v>45943.92922218596</v>
       </c>
       <c r="B189" t="n">
-        <v>16856.4</v>
+        <v>16702.8</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>BassanoBrescianoObservatory</t>
+          <t>Leavitt</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>16.83</v>
+        <v>16.63</v>
       </c>
       <c r="E189" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>10x30</t>
-        </is>
-      </c>
+          <t>Ic</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="n">
-        <v>42262</v>
+        <v>42333</v>
       </c>
       <c r="I189" t="b">
         <v>0</v>
@@ -6825,30 +6821,34 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>45943.934</v>
+        <v>45943.931</v>
       </c>
       <c r="B190" t="n">
-        <v>17115.6</v>
+        <v>16856.4</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Leavitt</t>
+          <t>BassanoBrescianoObservatory</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>16.63</v>
+        <v>16.83</v>
       </c>
       <c r="E190" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ic</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr"/>
+          <t>clear</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>10x30</t>
+        </is>
+      </c>
       <c r="H190" t="n">
-        <v>42333</v>
+        <v>42262</v>
       </c>
       <c r="I190" t="b">
         <v>0</v>
